--- a/diseases/d034/2005-2009.xlsx
+++ b/diseases/d034/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -24054,7 +24054,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25242,7 +25242,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27618,7 +27618,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31421,7 +31421,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32609,7 +32609,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33797,7 +33797,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -34985,7 +34985,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -37361,7 +37361,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -39737,7 +39737,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -40925,7 +40925,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42113,7 +42113,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43301,7 +43301,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -44489,7 +44489,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -45916,7 +45916,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47104,7 +47104,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48292,7 +48292,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49480,7 +49480,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50668,7 +50668,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -51856,7 +51856,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -53044,7 +53044,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -54232,7 +54232,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -55420,7 +55420,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -56608,7 +56608,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57796,7 +57796,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -58984,7 +58984,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -60411,7 +60411,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -61599,7 +61599,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -62787,7 +62787,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -63975,7 +63975,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -65163,7 +65163,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -66351,7 +66351,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -67539,7 +67539,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -68727,7 +68727,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -69915,7 +69915,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -71103,7 +71103,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -72291,7 +72291,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">

--- a/diseases/d034/2005-2009.xlsx
+++ b/diseases/d034/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -24054,7 +24054,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25242,7 +25242,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27618,7 +27618,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31421,7 +31421,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32609,7 +32609,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33797,7 +33797,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -34985,7 +34985,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -37361,7 +37361,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -39737,7 +39737,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -40925,7 +40925,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42113,7 +42113,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43301,7 +43301,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -44489,7 +44489,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -45916,7 +45916,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47104,7 +47104,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48292,7 +48292,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49480,7 +49480,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50668,7 +50668,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -51856,7 +51856,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -53044,7 +53044,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -54232,7 +54232,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -55420,7 +55420,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -56608,7 +56608,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57796,7 +57796,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -58984,7 +58984,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -60411,7 +60411,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -61599,7 +61599,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -62787,7 +62787,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -63975,7 +63975,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -65163,7 +65163,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -66351,7 +66351,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -67539,7 +67539,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -68727,7 +68727,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -69915,7 +69915,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -71103,7 +71103,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -72291,7 +72291,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">

--- a/diseases/d034/2005-2009.xlsx
+++ b/diseases/d034/2005-2009.xlsx
@@ -1161,9 +1161,6 @@
       <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -1796,9 +1793,6 @@
       <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -2588,9 +2582,6 @@
       <c r="O11" t="n">
         <v>10</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.1906184462995432</v>
       </c>
@@ -2984,9 +2975,6 @@
       <c r="O13" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -3776,9 +3764,6 @@
       <c r="O17" t="n">
         <v>16</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.3049895140792691</v>
       </c>
@@ -4172,9 +4157,6 @@
       <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -4964,9 +4946,6 @@
       <c r="O23" t="n">
         <v>13</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.2478039801894061</v>
       </c>
@@ -5360,9 +5339,6 @@
       <c r="O25" t="n">
         <v>4</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.08652158151068412</v>
       </c>
@@ -6152,9 +6128,6 @@
       <c r="O29" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.1906184462995432</v>
       </c>
@@ -6548,9 +6521,6 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -7340,9 +7310,6 @@
       <c r="O35" t="n">
         <v>14</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.2668658248193604</v>
       </c>
@@ -7736,9 +7703,6 @@
       <c r="O37" t="n">
         <v>3</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.06489118613301309</v>
       </c>
@@ -8528,9 +8492,6 @@
       <c r="O41" t="n">
         <v>8</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.1524947570396345</v>
       </c>
@@ -8924,9 +8885,6 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -9716,9 +9674,6 @@
       <c r="O47" t="n">
         <v>13</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.2478039801894061</v>
       </c>
@@ -10112,9 +10067,6 @@
       <c r="O49" t="n">
         <v>3</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.06489118613301309</v>
       </c>
@@ -10904,9 +10856,6 @@
       <c r="O53" t="n">
         <v>16</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.3049895140792691</v>
       </c>
@@ -11300,9 +11249,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -12092,9 +12038,6 @@
       <c r="O59" t="n">
         <v>15</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.2859276694493147</v>
       </c>
@@ -12488,9 +12431,6 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -13280,9 +13220,6 @@
       <c r="O65" t="n">
         <v>17</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.3240513587092234</v>
       </c>
@@ -13676,9 +13613,6 @@
       <c r="O67" t="n">
         <v>4</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.08652158151068412</v>
       </c>
@@ -14468,9 +14402,6 @@
       <c r="O71" t="n">
         <v>14</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.2668658248193604</v>
       </c>
@@ -14864,9 +14795,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -15656,9 +15584,6 @@
       <c r="O77" t="n">
         <v>13</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.2468551367658161</v>
       </c>
@@ -16291,9 +16216,6 @@
       <c r="O80" t="n">
         <v>4</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.08582781138651825</v>
       </c>
@@ -17083,9 +17005,6 @@
       <c r="O84" t="n">
         <v>12</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.2278662800915225</v>
       </c>
@@ -17479,9 +17398,6 @@
       <c r="O86" t="n">
         <v>4</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.08582781138651825</v>
       </c>
@@ -18271,9 +18187,6 @@
       <c r="O90" t="n">
         <v>11</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.208877423417229</v>
       </c>
@@ -18667,9 +18580,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -19459,9 +19369,6 @@
       <c r="O96" t="n">
         <v>12</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.2278662800915225</v>
       </c>
@@ -19855,9 +19762,6 @@
       <c r="O98" t="n">
         <v>4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.08582781138651825</v>
       </c>
@@ -20647,9 +20551,6 @@
       <c r="O102" t="n">
         <v>7</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.1329219967200548</v>
       </c>
@@ -21043,9 +20944,6 @@
       <c r="O104" t="n">
         <v>7</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.1501986699264069</v>
       </c>
@@ -21835,9 +21733,6 @@
       <c r="O108" t="n">
         <v>10</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.1898885667429354</v>
       </c>
@@ -22231,9 +22126,6 @@
       <c r="O110" t="n">
         <v>8</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.1716556227730365</v>
       </c>
@@ -23023,9 +22915,6 @@
       <c r="O114" t="n">
         <v>6</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.1139331400457613</v>
       </c>
@@ -23419,9 +23308,6 @@
       <c r="O116" t="n">
         <v>6</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.1287417170797774</v>
       </c>
@@ -24211,9 +24097,6 @@
       <c r="O120" t="n">
         <v>8</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.1519108533943483</v>
       </c>
@@ -24607,9 +24490,6 @@
       <c r="O122" t="n">
         <v>9</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.193112575619666</v>
       </c>
@@ -25399,9 +25279,6 @@
       <c r="O126" t="n">
         <v>15</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.2848328501144031</v>
       </c>
@@ -25795,9 +25672,6 @@
       <c r="O128" t="n">
         <v>6</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.1287417170797774</v>
       </c>
@@ -26587,9 +26461,6 @@
       <c r="O132" t="n">
         <v>13</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.2468551367658161</v>
       </c>
@@ -26983,9 +26854,6 @@
       <c r="O134" t="n">
         <v>5</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.1072847642331478</v>
       </c>
@@ -27775,9 +27643,6 @@
       <c r="O138" t="n">
         <v>13</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.2468551367658161</v>
       </c>
@@ -28171,9 +28036,6 @@
       <c r="O140" t="n">
         <v>9</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.193112575619666</v>
       </c>
@@ -28963,9 +28825,6 @@
       <c r="O144" t="n">
         <v>9</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.1708997100686419</v>
       </c>
@@ -29359,9 +29218,6 @@
       <c r="O146" t="n">
         <v>4</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.08582781138651825</v>
       </c>
@@ -30151,9 +30007,6 @@
       <c r="O150" t="n">
         <v>17</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.3214394436450477</v>
       </c>
@@ -30786,9 +30639,6 @@
       <c r="O153" t="n">
         <v>6</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.1274153165952079</v>
       </c>
@@ -31578,9 +31428,6 @@
       <c r="O157" t="n">
         <v>8</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.151265620538846</v>
       </c>
@@ -31974,9 +31821,6 @@
       <c r="O159" t="n">
         <v>11</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.2335947470912145</v>
       </c>
@@ -32766,9 +32610,6 @@
       <c r="O163" t="n">
         <v>6</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.1134492154041345</v>
       </c>
@@ -33162,9 +33003,6 @@
       <c r="O165" t="n">
         <v>4</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -33954,9 +33792,6 @@
       <c r="O169" t="n">
         <v>22</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.4159804564818264</v>
       </c>
@@ -34350,9 +34185,6 @@
       <c r="O171" t="n">
         <v>11</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.2335947470912145</v>
       </c>
@@ -35142,9 +34974,6 @@
       <c r="O175" t="n">
         <v>14</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.2647148359429804</v>
       </c>
@@ -35538,9 +35367,6 @@
       <c r="O177" t="n">
         <v>5</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.1061794304960066</v>
       </c>
@@ -36330,9 +36156,6 @@
       <c r="O181" t="n">
         <v>7</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.1323574179714902</v>
       </c>
@@ -36726,9 +36549,6 @@
       <c r="O183" t="n">
         <v>4</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -37518,9 +37338,6 @@
       <c r="O187" t="n">
         <v>22</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.4159804564818264</v>
       </c>
@@ -37914,9 +37731,6 @@
       <c r="O189" t="n">
         <v>3</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.06370765829760396</v>
       </c>
@@ -38706,9 +38520,6 @@
       <c r="O193" t="n">
         <v>11</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.2079902282409132</v>
       </c>
@@ -39102,9 +38913,6 @@
       <c r="O195" t="n">
         <v>4</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -39894,9 +39702,6 @@
       <c r="O199" t="n">
         <v>20</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.3781640513471149</v>
       </c>
@@ -40290,9 +40095,6 @@
       <c r="O201" t="n">
         <v>4</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -41082,9 +40884,6 @@
       <c r="O205" t="n">
         <v>24</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.4537968616165379</v>
       </c>
@@ -41478,9 +41277,6 @@
       <c r="O207" t="n">
         <v>5</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.1061794304960066</v>
       </c>
@@ -42270,9 +42066,6 @@
       <c r="O211" t="n">
         <v>19</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.3592558487797592</v>
       </c>
@@ -42666,9 +42459,6 @@
       <c r="O213" t="n">
         <v>2</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -43458,9 +43248,6 @@
       <c r="O217" t="n">
         <v>15</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.2836230385103362</v>
       </c>
@@ -43854,9 +43641,6 @@
       <c r="O219" t="n">
         <v>2</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -44646,9 +44430,6 @@
       <c r="O223" t="n">
         <v>10</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.1882042249213636</v>
       </c>
@@ -45281,9 +45062,6 @@
       <c r="O226" t="n">
         <v>4</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.08389084039956368</v>
       </c>
@@ -46073,9 +45851,6 @@
       <c r="O230" t="n">
         <v>22</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.4140492948269998</v>
       </c>
@@ -46469,9 +46244,6 @@
       <c r="O232" t="n">
         <v>2</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -47261,9 +47033,6 @@
       <c r="O236" t="n">
         <v>17</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.3199471823663181</v>
       </c>
@@ -47657,9 +47426,6 @@
       <c r="O238" t="n">
         <v>5</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -48449,9 +48215,6 @@
       <c r="O242" t="n">
         <v>23</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.4328697173191362</v>
       </c>
@@ -48845,9 +48608,6 @@
       <c r="O244" t="n">
         <v>4</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.08389084039956368</v>
       </c>
@@ -49637,9 +49397,6 @@
       <c r="O248" t="n">
         <v>19</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.3575880273505908</v>
       </c>
@@ -50033,9 +49790,6 @@
       <c r="O250" t="n">
         <v>7</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.1468089706992364</v>
       </c>
@@ -50825,9 +50579,6 @@
       <c r="O254" t="n">
         <v>21</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.3952288723348635</v>
       </c>
@@ -51221,9 +50972,6 @@
       <c r="O256" t="n">
         <v>5</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -52013,9 +51761,6 @@
       <c r="O260" t="n">
         <v>9</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.1693838024292272</v>
       </c>
@@ -52409,9 +52154,6 @@
       <c r="O262" t="n">
         <v>5</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -53201,9 +52943,6 @@
       <c r="O266" t="n">
         <v>22</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.4140492948269998</v>
       </c>
@@ -53597,9 +53336,6 @@
       <c r="O268" t="n">
         <v>6</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.1258362605993455</v>
       </c>
@@ -54389,9 +54125,6 @@
       <c r="O272" t="n">
         <v>19</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.3575880273505908</v>
       </c>
@@ -54785,9 +54518,6 @@
       <c r="O274" t="n">
         <v>8</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.1677816807991274</v>
       </c>
@@ -55577,9 +55307,6 @@
       <c r="O278" t="n">
         <v>14</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.263485914889909</v>
       </c>
@@ -55973,9 +55700,6 @@
       <c r="O280" t="n">
         <v>4</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.08389084039956368</v>
       </c>
@@ -56765,9 +56489,6 @@
       <c r="O284" t="n">
         <v>14</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.263485914889909</v>
       </c>
@@ -57161,9 +56882,6 @@
       <c r="O286" t="n">
         <v>2</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -57953,9 +57671,6 @@
       <c r="O290" t="n">
         <v>25</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.4705105623034089</v>
       </c>
@@ -58349,9 +58064,6 @@
       <c r="O292" t="n">
         <v>4</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.08389084039956368</v>
       </c>
@@ -59141,9 +58853,6 @@
       <c r="O296" t="n">
         <v>21</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.3933426568030064</v>
       </c>
@@ -59776,9 +59485,6 @@
       <c r="O299" t="n">
         <v>3</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.06212952037563508</v>
       </c>
@@ -60568,9 +60274,6 @@
       <c r="O303" t="n">
         <v>22</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.4120732595079115</v>
       </c>
@@ -60964,9 +60667,6 @@
       <c r="O305" t="n">
         <v>5</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.1035492006260585</v>
       </c>
@@ -61756,9 +61456,6 @@
       <c r="O309" t="n">
         <v>20</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.3746120540981014</v>
       </c>
@@ -62152,9 +61849,6 @@
       <c r="O311" t="n">
         <v>5</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.1035492006260585</v>
       </c>
@@ -62944,9 +62638,6 @@
       <c r="O315" t="n">
         <v>23</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.4308038622128165</v>
       </c>
@@ -63340,9 +63031,6 @@
       <c r="O317" t="n">
         <v>4</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0.08283936050084678</v>
       </c>
@@ -64132,9 +63820,6 @@
       <c r="O321" t="n">
         <v>17</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.3184202459833861</v>
       </c>
@@ -64528,9 +64213,6 @@
       <c r="O323" t="n">
         <v>6</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.1242590407512702</v>
       </c>
@@ -65320,9 +65002,6 @@
       <c r="O327" t="n">
         <v>18</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.3371508486882912</v>
       </c>
@@ -65716,9 +65395,6 @@
       <c r="O329" t="n">
         <v>9</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.1863885611269052</v>
       </c>
@@ -66508,9 +66184,6 @@
       <c r="O333" t="n">
         <v>11</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0.2060366297539557</v>
       </c>
@@ -66904,9 +66577,6 @@
       <c r="O335" t="n">
         <v>7</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0.1449688808764819</v>
       </c>
@@ -67696,9 +67366,6 @@
       <c r="O339" t="n">
         <v>12</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.2247672324588608</v>
       </c>
@@ -68092,9 +67759,6 @@
       <c r="O341" t="n">
         <v>10</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.2070984012521169</v>
       </c>
@@ -68884,9 +68548,6 @@
       <c r="O345" t="n">
         <v>15</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.280959040573576</v>
       </c>
@@ -69280,9 +68941,6 @@
       <c r="O347" t="n">
         <v>9</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0.1863885611269052</v>
       </c>
@@ -70072,9 +69730,6 @@
       <c r="O351" t="n">
         <v>10</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.1873060270490507</v>
       </c>
@@ -70468,9 +70123,6 @@
       <c r="O353" t="n">
         <v>8</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.1656787210016936</v>
       </c>
@@ -71260,9 +70912,6 @@
       <c r="O357" t="n">
         <v>13</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0.2434978351637659</v>
       </c>
@@ -71656,9 +71305,6 @@
       <c r="O359" t="n">
         <v>3</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0.06212952037563508</v>
       </c>
@@ -72448,9 +72094,6 @@
       <c r="O363" t="n">
         <v>17</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0.3184202459833861</v>
       </c>
@@ -72843,9 +72486,6 @@
       </c>
       <c r="O365" t="n">
         <v>7</v>
-      </c>
-      <c r="Q365" t="n">
-        <v>0</v>
       </c>
       <c r="R365" t="n">
         <v>0.1449688808764819</v>

--- a/diseases/d034/2005-2009.xlsx
+++ b/diseases/d034/2005-2009.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -19222,7 +19222,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20404,7 +20404,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31281,7 +31281,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -32463,7 +32463,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -33645,7 +33645,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -34827,7 +34827,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -36009,7 +36009,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -37191,7 +37191,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -39555,7 +39555,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -40737,7 +40737,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -41919,7 +41919,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -43101,7 +43101,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -45704,7 +45704,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -46886,7 +46886,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -48068,7 +48068,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -49250,7 +49250,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -50432,7 +50432,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -51614,7 +51614,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -52796,7 +52796,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53978,7 +53978,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -55160,7 +55160,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -56342,7 +56342,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -57524,7 +57524,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -58706,7 +58706,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -60127,7 +60127,7 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN302" t="b">
@@ -61309,7 +61309,7 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN308" t="b">
@@ -62491,7 +62491,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -63673,7 +63673,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -64855,7 +64855,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -66037,7 +66037,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -67219,7 +67219,7 @@
       </c>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN338" t="b">
@@ -68401,7 +68401,7 @@
       </c>
       <c r="AM344" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN344" t="b">
@@ -69583,7 +69583,7 @@
       </c>
       <c r="AM350" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN350" t="b">
@@ -70765,7 +70765,7 @@
       </c>
       <c r="AM356" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN356" t="b">
@@ -71947,7 +71947,7 @@
       </c>
       <c r="AM362" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN362" t="b">

--- a/diseases/d034/2005-2009.xlsx
+++ b/diseases/d034/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28668,7 +28668,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29850,7 +29850,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31271,7 +31271,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32453,7 +32453,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33635,7 +33635,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -34817,7 +34817,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -37181,7 +37181,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -38363,7 +38363,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -39545,7 +39545,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -40727,7 +40727,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -41909,7 +41909,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -44273,7 +44273,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -45694,7 +45694,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46876,7 +46876,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48058,7 +48058,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49240,7 +49240,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50422,7 +50422,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -51604,7 +51604,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52786,7 +52786,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53968,7 +53968,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -55150,7 +55150,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -56332,7 +56332,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57514,7 +57514,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -58696,7 +58696,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -60117,7 +60117,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -61299,7 +61299,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -62481,7 +62481,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -63663,7 +63663,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -64845,7 +64845,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -66027,7 +66027,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -67209,7 +67209,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -68391,7 +68391,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -69573,7 +69573,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -70755,7 +70755,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">

--- a/diseases/d034/2005-2009.xlsx
+++ b/diseases/d034/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28668,7 +28668,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29850,7 +29850,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31271,7 +31271,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32453,7 +32453,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33635,7 +33635,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -34817,7 +34817,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -37181,7 +37181,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -38363,7 +38363,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -39545,7 +39545,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -40727,7 +40727,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -41909,7 +41909,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -44273,7 +44273,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -45694,7 +45694,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46876,7 +46876,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48058,7 +48058,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49240,7 +49240,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50422,7 +50422,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -51604,7 +51604,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52786,7 +52786,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53968,7 +53968,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -55150,7 +55150,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -56332,7 +56332,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57514,7 +57514,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -58696,7 +58696,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -60117,7 +60117,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -61299,7 +61299,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -62481,7 +62481,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -63663,7 +63663,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -64845,7 +64845,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -66027,7 +66027,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -67209,7 +67209,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -68391,7 +68391,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -69573,7 +69573,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -70755,7 +70755,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">

--- a/diseases/d034/2005-2009.xlsx
+++ b/diseases/d034/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28668,7 +28668,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29850,7 +29850,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31271,7 +31271,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32453,7 +32453,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33635,7 +33635,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -34817,7 +34817,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -35999,7 +35999,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -37181,7 +37181,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -38363,7 +38363,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -39545,7 +39545,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -40727,7 +40727,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -41909,7 +41909,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -44273,7 +44273,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -45694,7 +45694,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46876,7 +46876,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48058,7 +48058,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49240,7 +49240,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50422,7 +50422,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -51604,7 +51604,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52786,7 +52786,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53968,7 +53968,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -55150,7 +55150,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -56332,7 +56332,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57514,7 +57514,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -58696,7 +58696,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -60117,7 +60117,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -61299,7 +61299,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -62481,7 +62481,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -63663,7 +63663,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -64845,7 +64845,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -66027,7 +66027,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -67209,7 +67209,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -68391,7 +68391,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -69573,7 +69573,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -70755,7 +70755,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -71937,7 +71937,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
